--- a/SGC-CKN/Excel/fdf1df28-3fc2-48d2-990b-59f93e731fa7_Thanh_Hoá_P2-71_D800_04-04-2026.xlsx
+++ b/SGC-CKN/Excel/fdf1df28-3fc2-48d2-990b-59f93e731fa7_Thanh_Hoá_P2-71_D800_04-04-2026.xlsx
@@ -112,7 +112,7 @@
     <t>2</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">09:35
@@ -122,7 +122,7 @@
     <t>3</t>
   </si>
   <si>
-    <t>Cát pha xám ghi, xám nâu TT dẻo</t>
+    <t>Cát pha, xám ghi, xám nâu, xám vàng, TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">10:05
@@ -142,7 +142,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
+    <t>Sét xám vàng, nâu vàng, xám xanh, TT nửa cứng</t>
   </si>
   <si>
     <t xml:space="preserve">13:20
@@ -152,7 +152,7 @@
     <t>6</t>
   </si>
   <si>
-    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
     <t xml:space="preserve">13:45
@@ -162,7 +162,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
+    <t>Cát thô, xám vàng, xám xanh, xám nâu, KC chặt</t>
   </si>
   <si>
     <t xml:space="preserve">14:50
@@ -172,7 +172,7 @@
     <t>8</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">18:00
@@ -328,17 +328,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
+        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFDE68A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
@@ -354,6 +349,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDD6FE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -499,35 +499,35 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1148,7 +1148,7 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>-1.6</v>
@@ -1157,10 +1157,10 @@
         <v>0.25</v>
       </c>
       <c r="I11" s="5">
-        <v>0.89</v>
+        <v>1.6</v>
       </c>
       <c r="J11" s="8">
-        <v>3.56</v>
+        <v>6.4</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1194,7 +1194,7 @@
       <c r="I12" s="9">
         <v>3.16</v>
       </c>
-      <c r="J12" s="12">
+      <c r="J12" s="8">
         <v>9.48</v>
       </c>
       <c r="K12" s="10" t="s">
@@ -1202,107 +1202,107 @@
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="12">
         <v>-4.76</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="12">
         <v>-8</v>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="12">
         <v>0.5</v>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="12">
         <v>3.24</v>
       </c>
-      <c r="J13" s="12">
+      <c r="J13" s="8">
         <v>6.48</v>
       </c>
-      <c r="K13" s="14" t="s">
+      <c r="K13" s="13" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="15">
         <v>-8</v>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="15">
         <v>-17</v>
       </c>
-      <c r="H14" s="16">
+      <c r="H14" s="15">
         <v>1.58</v>
       </c>
-      <c r="I14" s="16">
+      <c r="I14" s="15">
         <v>9</v>
       </c>
-      <c r="J14" s="12">
+      <c r="J14" s="8">
         <v>5.68</v>
       </c>
-      <c r="K14" s="17" t="s">
+      <c r="K14" s="16" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="21" t="s">
+      <c r="D15" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="E15" s="21" t="s">
+      <c r="E15" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="F15" s="19">
+      <c r="F15" s="18">
         <v>-17</v>
       </c>
-      <c r="G15" s="19">
+      <c r="G15" s="18">
         <v>-22</v>
       </c>
-      <c r="H15" s="19">
+      <c r="H15" s="18">
         <v>1.67</v>
       </c>
-      <c r="I15" s="19">
+      <c r="I15" s="18">
         <v>5</v>
       </c>
-      <c r="J15" s="8">
+      <c r="J15" s="21">
         <v>3</v>
       </c>
-      <c r="K15" s="20" t="s">
+      <c r="K15" s="19" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       <c r="I16" s="22">
         <v>4</v>
       </c>
-      <c r="J16" s="12">
+      <c r="J16" s="8">
         <v>9.6</v>
       </c>
       <c r="K16" s="23" t="s">
@@ -1369,7 +1369,7 @@
       <c r="I17" s="25">
         <v>13.5</v>
       </c>
-      <c r="J17" s="12">
+      <c r="J17" s="8">
         <v>12.46</v>
       </c>
       <c r="K17" s="26" t="s">
@@ -1404,7 +1404,7 @@
       <c r="I18" s="28">
         <v>4.64</v>
       </c>
-      <c r="J18" s="8">
+      <c r="J18" s="21">
         <v>1.47</v>
       </c>
       <c r="K18" s="29" t="s">
@@ -1560,7 +1560,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>-1.6</v>
@@ -1569,10 +1569,10 @@
         <v>0.25</v>
       </c>
       <c r="H2" s="5">
-        <v>0.89</v>
+        <v>1.6</v>
       </c>
       <c r="I2" s="8">
-        <v>3.56</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1600,94 +1600,94 @@
       <c r="H3" s="9">
         <v>3.16</v>
       </c>
-      <c r="I3" s="12">
+      <c r="I3" s="8">
         <v>9.48</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="13">
+      <c r="A4" s="12">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="12">
         <v>1</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="12">
         <v>-4.76</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="12">
         <v>-8</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="12">
         <v>0.5</v>
       </c>
-      <c r="H4" s="13">
+      <c r="H4" s="12">
         <v>3.24</v>
       </c>
-      <c r="I4" s="12">
+      <c r="I4" s="8">
         <v>6.48</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="16">
+      <c r="A5" s="15">
         <v>4</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="15">
         <v>1</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="15">
         <v>-8</v>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="15">
         <v>-17</v>
       </c>
-      <c r="G5" s="16">
+      <c r="G5" s="15">
         <v>1.58</v>
       </c>
-      <c r="H5" s="16">
+      <c r="H5" s="15">
         <v>9</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="8">
         <v>5.68</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="19">
+      <c r="A6" s="18">
         <v>5</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="18">
         <v>1</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="18">
         <v>-17</v>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="18">
         <v>-22</v>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="18">
         <v>1.67</v>
       </c>
-      <c r="H6" s="19">
+      <c r="H6" s="18">
         <v>5</v>
       </c>
-      <c r="I6" s="8">
+      <c r="I6" s="21">
         <v>3</v>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       <c r="H7" s="22">
         <v>4</v>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="8">
         <v>9.6</v>
       </c>
     </row>
@@ -1745,7 +1745,7 @@
       <c r="H8" s="25">
         <v>13.5</v>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="8">
         <v>12.46</v>
       </c>
     </row>
@@ -1774,7 +1774,7 @@
       <c r="H9" s="28">
         <v>4.64</v>
       </c>
-      <c r="I9" s="8">
+      <c r="I9" s="21">
         <v>1.47</v>
       </c>
     </row>
@@ -1792,7 +1792,7 @@
         <v>8</v>
       </c>
       <c r="E10" s="33">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="F10" s="33">
         <v>-44.14</v>
@@ -1801,10 +1801,10 @@
         <v>9</v>
       </c>
       <c r="H10" s="33">
-        <v>43.43</v>
+        <v>44.14</v>
       </c>
       <c r="I10" s="33">
-        <v>4.83</v>
+        <v>4.9</v>
       </c>
     </row>
   </sheetData>
